--- a/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4728508-FC3B-46C2-BBF5-6C88C58E8A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{D4728508-FC3B-46C2-BBF5-6C88C58E8A52}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
   </bookViews>
   <sheets>
-    <sheet name="SearchButton" sheetId="1" r:id="rId1"/>
+    <sheet name="SearchButton" r:id="rId1" sheetId="1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
   <si>
     <t>Result</t>
   </si>
@@ -102,12 +102,25 @@
   </si>
   <si>
     <t>Wed Feb 04 12:58:06 IST 2026</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:18:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:18:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:19:05 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -166,28 +179,28 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -204,10 +217,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -242,7 +255,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -294,7 +307,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -405,21 +418,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -436,7 +449,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -508,27 +521,27 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:L4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.36328125" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="26.54296875" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="35.453125" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="18.7265625" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.453125" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="10.6328125" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="26.54296875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="7.6328125" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="7.6328125" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="27.90625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" width="6.36328125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="26.54296875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="35.453125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" width="18.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" width="9.453125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" width="10.6328125" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="26.54296875" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" width="7.6328125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" width="7.6328125" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="27.90625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -566,12 +579,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row customFormat="1" r="2" s="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>15</v>
@@ -581,12 +594,12 @@
       </c>
       <c r="L2" s="4"/>
     </row>
-    <row r="3" spans="1:12" s="2" customFormat="1" ht="13" x14ac:dyDescent="0.25">
+    <row customFormat="1" ht="13" r="3" s="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>16</v>
@@ -599,12 +612,12 @@
       </c>
       <c r="L3" s="4"/>
     </row>
-    <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row customFormat="1" r="4" s="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
@@ -625,7 +638,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="32">
   <si>
     <t>Result</t>
   </si>
@@ -114,6 +114,24 @@
   </si>
   <si>
     <t>Tue Feb 17 12:19:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 15:25:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 15:25:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 15:25:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:17:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:17:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:18:21 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -584,7 +602,7 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>15</v>
@@ -599,7 +617,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>16</v>
@@ -617,7 +635,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>

--- a/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="35">
   <si>
     <t>Result</t>
   </si>
@@ -132,6 +132,15 @@
   </si>
   <si>
     <t>Mon Feb 23 17:18:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 16:42:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 16:43:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 16:44:03 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -602,7 +611,7 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>15</v>
@@ -617,7 +626,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>16</v>
@@ -635,7 +644,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>

--- a/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="38">
   <si>
     <t>Result</t>
   </si>
@@ -141,6 +141,15 @@
   </si>
   <si>
     <t>Wed Mar 11 16:44:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 16:59:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:00:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:01:10 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -611,7 +620,7 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>15</v>
@@ -626,7 +635,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>16</v>
@@ -644,7 +653,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>

--- a/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="41">
   <si>
     <t>Result</t>
   </si>
@@ -150,6 +150,15 @@
   </si>
   <si>
     <t>Wed Mar 25 17:01:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:25:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:26:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:26:37 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -620,7 +629,7 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>15</v>
@@ -635,7 +644,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>16</v>
@@ -653,7 +662,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>

--- a/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="47">
   <si>
     <t>Result</t>
   </si>
@@ -159,6 +159,24 @@
   </si>
   <si>
     <t>Thu Apr 30 14:26:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 17:43:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 17:44:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 17:45:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:06:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:07:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:07:51 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -629,7 +647,7 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>15</v>
@@ -644,7 +662,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>16</v>
@@ -662,7 +680,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>

--- a/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_SearchButton.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="50">
   <si>
     <t>Result</t>
   </si>
@@ -177,6 +177,15 @@
   </si>
   <si>
     <t>Thu Jun 18 03:07:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:13:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:14:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:15:01 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -592,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="6.36328125" collapsed="true"/>
@@ -643,11 +652,11 @@
       </c>
     </row>
     <row customFormat="1" r="2" s="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="B2" t="s">
-        <v>44</v>
+      <c r="B2" t="s" s="0">
+        <v>47</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>15</v>
@@ -658,11 +667,11 @@
       <c r="L2" s="4"/>
     </row>
     <row customFormat="1" ht="13" r="3" s="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="B3" t="s">
-        <v>45</v>
+      <c r="B3" t="s" s="0">
+        <v>48</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>16</v>
@@ -676,11 +685,11 @@
       <c r="L3" s="4"/>
     </row>
     <row customFormat="1" r="4" s="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="B4" t="s">
-        <v>46</v>
+      <c r="B4" t="s" s="0">
+        <v>49</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
